--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-india\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0272168-C612-4468-B6F1-A4C20A325B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B572B393-2293-47FB-8029-7D485036E872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -184,9 +184,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -224,9 +224,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -259,26 +259,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -311,26 +294,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -613,25 +579,32 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>5.0999999999999997E-2</v>
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C2">
-        <v>5.0999999999999997E-2</v>
+        <f t="shared" ref="C2:H2" si="0">1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D2">
-        <v>5.0999999999999997E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E2">
-        <v>5.0999999999999997E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F2">
-        <v>5.0999999999999997E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G2">
-        <v>5.0999999999999997E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H2">
-        <v>5.0999999999999997E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -639,25 +612,25 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>9.6000000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="C3">
-        <v>9.6000000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="D3">
-        <v>9.6000000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="E3">
-        <v>9.6000000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="F3">
-        <v>9.6000000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G3">
-        <v>9.6000000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="H3">
-        <v>9.6000000000000002E-2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -665,25 +638,25 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>4.4999999999999998E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
       <c r="C4">
-        <v>4.4999999999999998E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
       <c r="D4">
-        <v>4.4999999999999998E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
       <c r="E4">
-        <v>4.4999999999999998E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
       <c r="F4">
-        <v>4.4999999999999998E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
       <c r="G4">
-        <v>4.4999999999999998E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
       <c r="H4">
-        <v>4.4999999999999998E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -691,25 +664,25 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="C5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="D5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="E5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="F5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="G5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="H5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -717,25 +690,25 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.3</v>
+        <v>2.9819999999999999E-2</v>
       </c>
       <c r="C6">
-        <v>0.3</v>
+        <v>2.9819999999999999E-2</v>
       </c>
       <c r="D6">
-        <v>0.3</v>
+        <v>2.9819999999999999E-2</v>
       </c>
       <c r="E6">
-        <v>0.3</v>
+        <v>2.9819999999999999E-2</v>
       </c>
       <c r="F6">
-        <v>0.3</v>
+        <v>2.9819999999999999E-2</v>
       </c>
       <c r="G6">
-        <v>0.3</v>
+        <v>2.9819999999999999E-2</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>2.9819999999999999E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -743,25 +716,25 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="C7">
-        <v>0.1</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="D7">
-        <v>0.1</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="E7">
-        <v>0.1</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="F7">
-        <v>0.1</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="G7">
-        <v>0.1</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>5.8500000000000003E-2</v>
       </c>
     </row>
   </sheetData>
@@ -812,25 +785,25 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0.1</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="C2">
-        <v>0.1</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="D2">
-        <v>0.1</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="E2">
-        <v>0.1</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="F2">
-        <v>0.1</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>7.1999999999999995E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -838,25 +811,25 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.1</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="C3">
-        <v>0.1</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="D3">
-        <v>0.1</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="E3">
-        <v>0.1</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="F3">
-        <v>0.1</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="H3">
-        <v>0.1</v>
+        <v>5.7500000000000002E-2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -864,25 +837,25 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>3.125E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="C4">
-        <v>3.125E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="D4">
-        <v>3.125E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="E4">
-        <v>3.125E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="F4">
-        <v>3.125E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="G4">
-        <v>3.125E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="H4">
-        <v>3.125E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -890,25 +863,25 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="C5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="D5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="E5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="F5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="G5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="H5">
-        <v>2.8570999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -916,25 +889,25 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>3.0303E-2</v>
+        <v>3.0300000000000001E-2</v>
       </c>
       <c r="C6">
-        <v>3.0303E-2</v>
+        <v>3.0300000000000001E-2</v>
       </c>
       <c r="D6">
-        <v>3.0303E-2</v>
+        <v>3.0300000000000001E-2</v>
       </c>
       <c r="E6">
-        <v>3.0303E-2</v>
+        <v>3.0300000000000001E-2</v>
       </c>
       <c r="F6">
-        <v>3.0303E-2</v>
+        <v>3.0300000000000001E-2</v>
       </c>
       <c r="G6">
-        <v>3.0303E-2</v>
+        <v>3.0300000000000001E-2</v>
       </c>
       <c r="H6">
-        <v>3.0303E-2</v>
+        <v>3.0300000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -942,25 +915,25 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B572B393-2293-47FB-8029-7D485036E872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B539881-35F2-4ACF-93AE-EB11A251A4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -785,25 +785,32 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>7.1999999999999995E-2</v>
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" ref="C2:H2" si="0">1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -811,25 +818,32 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>5.7500000000000002E-2</v>
+        <f>1/19</f>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="C3">
-        <v>5.7500000000000002E-2</v>
+        <f t="shared" ref="C3:H3" si="1">1/19</f>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="D3">
-        <v>5.7500000000000002E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="E3">
-        <v>5.7500000000000002E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="F3">
-        <v>5.7500000000000002E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="G3">
-        <v>5.7500000000000002E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="H3">
-        <v>5.7500000000000002E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2631578947368418E-2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
